--- a/output/pdf_financials_xlsx/VCU.xlsx
+++ b/output/pdf_financials_xlsx/VCU.xlsx
@@ -2475,16 +2475,16 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.637814</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.981157</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.540412</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.016207</v>
       </c>
     </row>
     <row r="93">
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.015912</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>-0.323435</v>
@@ -3995,7 +3995,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -5253,7 +5257,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -11231,7 +11239,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E190" s="5" t="n">
         <v>-0.015912</v>
       </c>

--- a/output/pdf_financials_xlsx/VCU.xlsx
+++ b/output/pdf_financials_xlsx/VCU.xlsx
@@ -1181,16 +1181,16 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.573316</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.170113</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.780746</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.35554</v>
       </c>
     </row>
     <row r="35">
@@ -1225,16 +1225,16 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.573316</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.170113</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.780746</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.35554</v>
       </c>
     </row>
     <row r="37">
@@ -1489,16 +1489,16 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.604498</v>
+        <v>0.031182</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.273027</v>
+        <v>0.102914</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.916699</v>
+        <v>0.135953</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.509121</v>
+        <v>0.153581</v>
       </c>
     </row>
     <row r="49">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">

--- a/output/pdf_financials_xlsx/VCU.xlsx
+++ b/output/pdf_financials_xlsx/VCU.xlsx
@@ -565,13 +565,13 @@
         <v>0.468401</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.575771</v>
+        <v>0.662626</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.692252</v>
+        <v>0.778606</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.783767</v>
+        <v>0.9121</v>
       </c>
     </row>
     <row r="8">
@@ -760,10 +760,10 @@
         <v>-0.151656</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-2.354244</v>
+        <v>-2.051412</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-2.24951</v>
+        <v>-2.018231</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-13.110385</v>
@@ -782,10 +782,10 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.302832</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.231279</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1022,10 +1022,10 @@
         <v>-0.151656</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.354244</v>
+        <v>-2.051412</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.24951</v>
+        <v>-2.018231</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-13.110385</v>
@@ -1066,10 +1066,10 @@
         <v>-0.151656</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.354244</v>
+        <v>-2.051412</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.24951</v>
+        <v>-2.018231</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-13.110385</v>
@@ -1120,10 +1120,10 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-14.76212481939269</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-11.45949100970107</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -2658,16 +2658,16 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002108</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.048748</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.02944</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.016214</v>
       </c>
     </row>
     <row r="102">
@@ -2768,16 +2768,16 @@
         <v>0</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.372093</v>
+        <v>0.369985</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.417795</v>
+        <v>-0.466543</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.357218</v>
+        <v>-0.327778</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.115542</v>
+        <v>-0.099328</v>
       </c>
     </row>
     <row r="107">
@@ -5675,7 +5675,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -5714,7 +5718,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -6147,7 +6155,11 @@
           <t>Proceeds from issuance of flow-through units in private placement</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -6188,7 +6200,11 @@
           <t>Proceeds from issuance of flow-through shares in private placement</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -9903,7 +9919,11 @@
           <t>Proceeds from issuance of common shares in private placement</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -12546,7 +12566,11 @@
           <t>Director fees 12</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -13293,7 +13317,11 @@
           <t>Director fees 13</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -13990,7 +14018,11 @@
           <t>Income tax recovery 12</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -14330,7 +14362,11 @@
           <t>Income tax recovery 11</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
